--- a/jogos_2025-02-03.xlsx
+++ b/jogos_2025-02-03.xlsx
@@ -762,35 +762,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Paraguay Division Profesional</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSIS Semarang</t>
+          <t>2 de Mayo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Guaraní</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.71</v>
+        <v>2.97</v>
       </c>
       <c r="M3" t="n">
-        <v>3.47</v>
+        <v>2.78</v>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="O3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="X3" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.11</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['37', '45', '49', '90+4']</t>
+          <t>['45+2', '53']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45691.375</v>
@@ -891,119 +891,119 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paraguay Division Profesional</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2 de Mayo</t>
+          <t>PSIS Semarang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guaraní</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.97</v>
+        <v>3.71</v>
       </c>
       <c r="M4" t="n">
-        <v>2.78</v>
+        <v>3.47</v>
       </c>
       <c r="N4" t="n">
-        <v>2.67</v>
+        <v>1.95</v>
       </c>
       <c r="O4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
       <c r="R4" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['37', '45', '49', '90+4']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.25</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['45+2', '53']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AI4" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45691.375</v>
@@ -1288,16 +1288,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Enugu Rangers</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Katsina United</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Z7" t="n">
         <v>1.38</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="N7" t="n">
-        <v>7.74</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>7</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W7" t="n">
+      <c r="AA7" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI7" t="n">
         <v>1.44</v>
       </c>
-      <c r="X7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['45', '89']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45691.5</v>
@@ -1417,16 +1417,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Enugu Rangers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Katsina United</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="M8" t="n">
-        <v>3.18</v>
+        <v>3.82</v>
       </c>
       <c r="N8" t="n">
-        <v>5.85</v>
+        <v>7.74</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="X8" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.72</v>
+        <v>2.31</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.95</v>
+        <v>4.3</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['45', '89']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
         <v>1.07</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AH8" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45691.5</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,19 +1933,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.23</v>
+        <v>7.54</v>
       </c>
       <c r="M12" t="n">
-        <v>3.03</v>
+        <v>4.94</v>
       </c>
       <c r="N12" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="P12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['31', '46']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45691.58333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,19 +2062,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>7.54</v>
+        <v>4.23</v>
       </c>
       <c r="M13" t="n">
-        <v>4.94</v>
+        <v>3.03</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.87</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['31', '46']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.8</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['5']</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45691.58333333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.73</v>
+        <v>2.17</v>
       </c>
       <c r="M15" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.81</v>
+        <v>3.47</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="T15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U15" t="n">
         <v>1.25</v>
       </c>
       <c r="V15" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="X15" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['35', '88']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['14', '26', '85']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45691.625</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.17</v>
+        <v>2.73</v>
       </c>
       <c r="M16" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="N16" t="n">
-        <v>3.47</v>
+        <v>2.81</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="T16" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U16" t="n">
         <v>1.25</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X16" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['35', '88']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['14', '26', '85']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45691.625</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="M21" t="n">
-        <v>3.37</v>
+        <v>4.6</v>
       </c>
       <c r="N21" t="n">
-        <v>4.75</v>
+        <v>6.8</v>
       </c>
       <c r="O21" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.3</v>
       </c>
-      <c r="V21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.33</v>
       </c>
-      <c r="X21" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="AC21" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="AD21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>4</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>3.1</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45691.6875</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="M22" t="n">
-        <v>4.6</v>
+        <v>3.37</v>
       </c>
       <c r="N22" t="n">
-        <v>6.8</v>
+        <v>4.75</v>
       </c>
       <c r="O22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH22" t="n">
         <v>2</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>7</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['8']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AI22" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45691.6875</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.75</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="U23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="AD23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.36</v>
       </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['56']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['41', '64']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AI23" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45691.69791666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9</v>
+        <v>3.58</v>
       </c>
       <c r="N24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['41', '64']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI24" t="n">
         <v>2.5</v>
       </c>
-      <c r="O24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD24" t="n">
+      <c r="AJ24" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['49']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.95</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45691.69791666666</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Central Córdoba SdE</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="N25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S25" t="n">
         <v>4</v>
       </c>
-      <c r="O25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="V25" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>2.9</v>
+        <v>6.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="Z25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC25" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA25" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2</v>
-      </c>
       <c r="AD25" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['65', '79']</t>
+          <t>['64', '74']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.68</v>
+        <v>2.95</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45691.70833333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3754,10 +3754,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="M26" t="n">
-        <v>5.8</v>
+        <v>4.13</v>
       </c>
       <c r="N26" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="P26" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X26" t="n">
         <v>4</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X26" t="n">
-        <v>6.4</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.37</v>
+        <v>3.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AD26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['8', '79']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH26" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['64', '74']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['42']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AI26" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45691.70833333334</v>
@@ -3858,35 +3858,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Central Córdoba SdE</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>3.04</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="R27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.4</v>
       </c>
-      <c r="S27" t="n">
+      <c r="X27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['65', '79']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>2.75</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['11', '59']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['33', '51', '87']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45691.70833333334</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.63</v>
+        <v>2.21</v>
       </c>
       <c r="M28" t="n">
-        <v>4.13</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>5.5</v>
+        <v>3.04</v>
       </c>
       <c r="O28" t="n">
+        <v>3</v>
+      </c>
+      <c r="P28" t="n">
         <v>2.2</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q28" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="X28" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['8', '79']</t>
+          <t>['11', '59']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['33', '51', '87']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45691.70833333334</v>
@@ -4384,16 +4384,16 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -4410,65 +4410,65 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="S31" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="T31" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="W31" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="X31" t="n">
-        <v>3.42</v>
+        <v>2.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.69</v>
+        <v>6.32</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['34', '58']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45691.80208333334</v>
@@ -4513,16 +4513,16 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -4539,65 +4539,65 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="M32" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y32" t="n">
         <v>2.1</v>
       </c>
-      <c r="T32" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W32" t="n">
+      <c r="Z32" t="n">
         <v>1.7</v>
       </c>
-      <c r="X32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AA32" t="n">
-        <v>6.32</v>
+        <v>3.69</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['34', '58']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45691.80208333334</v>
